--- a/iml_data_analysis/sample_data/employee_20240806.xlsx
+++ b/iml_data_analysis/sample_data/employee_20240806.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univie365-my.sharepoint.com/personal/steyrld69_univie_ac_at/Documents/T1 IML/scripts/sample_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univie365-my.sharepoint.com/personal/steyrld69_univie_ac_at/Documents/T1 IML/scr/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{BE091500-13A7-42D3-ADA7-DA067991E293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA853199-1BE7-4E4A-B32C-8231689BBAC4}"/>
@@ -145,10 +145,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
